--- a/StructureDefinition-pharmac-charge-item-definition.xlsx
+++ b/StructureDefinition-pharmac-charge-item-definition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -672,6 +672,70 @@
   </si>
   <si>
     <t>Indicates whether this item is only subsidised when used in combination with other medicines or treatments.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:authorizationSchema</t>
+  </si>
+  <si>
+    <t>authorizationSchema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/authorization-schema}
+</t>
+  </si>
+  <si>
+    <t>JSON Schema for authorization form</t>
+  </si>
+  <si>
+    <t>Base64-encoded JSON Schema that defines the structure and validation rules for the Special Authorization application form. Clients should base64-decode the value to obtain the JSON Schema.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:PricingSection29</t>
+  </si>
+  <si>
+    <t>PricingSection29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/pricing-section-29}
+</t>
+  </si>
+  <si>
+    <t>Pricing Section 29</t>
+  </si>
+  <si>
+    <t>Indicates whether Section 29 applies to this pricing record.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:PricingNotCombined</t>
+  </si>
+  <si>
+    <t>PricingNotCombined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/pricing-not-combined}
+</t>
+  </si>
+  <si>
+    <t>Pricing Not Combined</t>
+  </si>
+  <si>
+    <t>Indicates whether Not Combined applies to this pricing record.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:PricingCoPaymentMax</t>
+  </si>
+  <si>
+    <t>PricingCoPaymentMax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/pricing-copayment-max}
+</t>
+  </si>
+  <si>
+    <t>Pricing Co-Payment Max</t>
+  </si>
+  <si>
+    <t>Indicates whether Co-Payment Max applies to this pricing record.</t>
   </si>
   <si>
     <t>ChargeItemDefinition.modifierExtension</t>
@@ -1718,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN75"/>
+  <dimension ref="A1:AN79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.1171875" customWidth="true" bestFit="true"/>
@@ -4389,43 +4453,41 @@
         <v>209</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4473,7 +4535,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4482,13 +4544,13 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -4500,35 +4562,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>217</v>
@@ -4536,12 +4600,8 @@
       <c r="M25" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4589,28 +4649,28 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -4618,12 +4678,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4632,7 +4694,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4641,23 +4703,19 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4705,7 +4763,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4714,32 +4772,34 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4751,26 +4811,24 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4819,73 +4877,75 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>240</v>
-      </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4933,25 +4993,25 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4960,12 +5020,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4973,13 +5033,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4991,13 +5051,17 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5045,13 +5109,13 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -5063,10 +5127,10 @@
         <v>85</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5074,14 +5138,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5100,16 +5164,20 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5157,7 +5225,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5175,16 +5243,16 @@
         <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>251</v>
       </c>
@@ -5193,17 +5261,17 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5212,7 +5280,7 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>253</v>
@@ -5220,7 +5288,9 @@
       <c r="M31" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N31" s="2"/>
+      <c r="N31" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5275,7 +5345,7 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5287,10 +5357,10 @@
         <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5298,10 +5368,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5309,7 +5379,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>87</v>
@@ -5318,22 +5388,22 @@
         <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>252</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5359,13 +5429,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5383,10 +5453,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>87</v>
@@ -5404,7 +5474,7 @@
         <v>262</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5412,10 +5482,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5426,7 +5496,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5438,20 +5508,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5499,13 +5565,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5517,10 +5583,10 @@
         <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5528,21 +5594,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5554,17 +5620,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5613,13 +5677,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5631,35 +5695,35 @@
         <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5668,20 +5732,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5729,13 +5789,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5747,10 +5807,10 @@
         <v>85</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -5758,10 +5818,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5769,31 +5829,31 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5819,13 +5879,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5843,13 +5903,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5861,21 +5921,21 @@
         <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5889,7 +5949,7 @@
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5898,18 +5958,20 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5957,7 +6019,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5975,10 +6037,10 @@
         <v>85</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -5986,21 +6048,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6012,20 +6074,18 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6073,13 +6133,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6091,21 +6151,21 @@
         <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6116,10 +6176,10 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6128,18 +6188,20 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6163,13 +6225,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6187,13 +6249,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6205,55 +6267,55 @@
         <v>85</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6301,13 +6363,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6319,21 +6381,21 @@
         <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6347,25 +6409,25 @@
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6415,7 +6477,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6433,21 +6495,21 @@
         <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6458,7 +6520,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6467,22 +6529,22 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6531,13 +6593,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6549,21 +6611,21 @@
         <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6574,7 +6636,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6586,20 +6648,18 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6623,13 +6683,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6647,13 +6707,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6665,25 +6725,25 @@
         <v>85</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6693,25 +6753,27 @@
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6735,13 +6797,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6759,7 +6821,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6777,21 +6839,21 @@
         <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6802,10 +6864,10 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -6814,16 +6876,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6873,13 +6935,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6891,21 +6953,21 @@
         <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6916,10 +6978,10 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -6928,18 +6990,20 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6987,13 +7051,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7005,21 +7069,21 @@
         <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7039,19 +7103,23 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>353</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7099,7 +7167,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7111,60 +7179,58 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7189,13 +7255,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7213,22 +7279,22 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
@@ -7240,16 +7306,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7259,29 +7325,27 @@
         <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>366</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7329,7 +7393,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7341,7 +7405,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>85</v>
@@ -7356,12 +7420,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7369,13 +7433,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7384,15 +7448,17 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7441,13 +7507,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7470,10 +7536,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7496,13 +7562,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7553,7 +7619,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7565,10 +7631,10 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7582,21 +7648,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7608,16 +7674,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>378</v>
+        <v>233</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7667,22 +7733,22 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7694,16 +7760,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7713,25 +7779,29 @@
         <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7779,7 +7849,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7791,7 +7861,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>85</v>
@@ -7808,10 +7878,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7819,7 +7889,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
@@ -7834,13 +7904,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7891,7 +7961,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7903,10 +7973,10 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7920,21 +7990,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7946,17 +8016,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8005,22 +8073,22 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -8034,46 +8102,44 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8121,19 +8187,19 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -8148,12 +8214,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8167,7 +8233,7 @@
         <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8176,17 +8242,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8235,7 +8299,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8264,10 +8328,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8290,13 +8354,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8347,7 +8411,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8362,7 +8426,7 @@
         <v>21</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8376,14 +8440,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8405,13 +8469,13 @@
         <v>131</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8461,7 +8525,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8476,7 +8540,7 @@
         <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
@@ -8490,14 +8554,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8519,16 +8583,16 @@
         <v>131</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8577,7 +8641,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8606,10 +8670,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8617,10 +8681,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8632,15 +8696,17 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8689,13 +8755,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -8718,10 +8784,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8744,13 +8810,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8801,7 +8867,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8813,10 +8879,10 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -8830,21 +8896,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8856,16 +8922,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>378</v>
+        <v>233</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8915,22 +8981,22 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
@@ -8942,16 +9008,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8961,25 +9027,29 @@
         <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9027,7 +9097,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9039,7 +9109,7 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>85</v>
@@ -9056,10 +9126,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9067,7 +9137,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>87</v>
@@ -9082,13 +9152,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>356</v>
+        <v>412</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9139,7 +9209,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9151,10 +9221,10 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
@@ -9168,21 +9238,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9194,17 +9264,15 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9253,22 +9321,22 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
@@ -9282,46 +9350,44 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9369,19 +9435,19 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -9398,10 +9464,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9409,10 +9475,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>88</v>
@@ -9424,13 +9490,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>371</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9457,13 +9523,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -9481,13 +9547,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -9510,10 +9576,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9521,7 +9587,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>87</v>
@@ -9536,13 +9602,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9593,7 +9659,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9605,10 +9671,10 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9622,21 +9688,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9648,15 +9714,17 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9705,22 +9773,22 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9734,14 +9802,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>210</v>
+        <v>385</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9754,24 +9822,26 @@
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9807,19 +9877,19 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9834,7 +9904,7 @@
         <v>137</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>359</v>
+        <v>85</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -9846,12 +9916,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9859,35 +9929,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>418</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9911,13 +9977,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -9935,13 +10001,13 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
@@ -9950,7 +10016,7 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9964,10 +10030,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9987,23 +10053,19 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10051,7 +10113,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10066,7 +10128,7 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>431</v>
+        <v>85</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
@@ -10080,10 +10142,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10106,13 +10168,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>376</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10163,7 +10225,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10175,10 +10237,10 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10192,21 +10254,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10218,15 +10280,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>437</v>
+        <v>131</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10263,47 +10327,503 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK75" t="s" s="2">
+      <c r="AK77" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AL78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN75">
+  <autoFilter ref="A1:AN79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10313,7 +10833,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-pharmac-charge-item-definition.xlsx
+++ b/StructureDefinition-pharmac-charge-item-definition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-pharmac-charge-item-definition.xlsx
+++ b/StructureDefinition-pharmac-charge-item-definition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -655,7 +655,7 @@
     <t>Statim (urgent dispensing) flag</t>
   </si>
   <si>
-    <t>Indicates whether stat (urgent) dispensing rules apply for this item.</t>
+    <t>Indicates whether stat (urgent) dispensing rules apply for this medication.</t>
   </si>
   <si>
     <t>ChargeItemDefinition.extension:inCombination</t>
@@ -671,7 +671,7 @@
     <t>In-combination funding flag</t>
   </si>
   <si>
-    <t>Indicates whether this item is only subsidised when used in combination with other medicines or treatments.</t>
+    <t>Indicates whether this medication is only subsidised when used in combination with other medicines.</t>
   </si>
   <si>
     <t>ChargeItemDefinition.extension:authorizationSchema</t>
@@ -688,6 +688,38 @@
   </si>
   <si>
     <t>Base64-encoded JSON Schema that defines the structure and validation rules for the Special Authorization application form. Clients should base64-decode the value to obtain the JSON Schema.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:fundingSubsidyAmount</t>
+  </si>
+  <si>
+    <t>fundingSubsidyAmount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/funding-subsidy-amount}
+</t>
+  </si>
+  <si>
+    <t>Structured subsidy details</t>
+  </si>
+  <si>
+    <t>Structured subsidy metadata including subsidy type, status, optional amount, and display label.</t>
+  </si>
+  <si>
+    <t>ChargeItemDefinition.extension:scheduleFundingAttributes</t>
+  </si>
+  <si>
+    <t>scheduleFundingAttributes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/schedule-funding-attributes}
+</t>
+  </si>
+  <si>
+    <t>Grouped schedule funding attributes</t>
+  </si>
+  <si>
+    <t>Grouped funding attributes including contract markers, dispensing flags, and co-payment markers.</t>
   </si>
   <si>
     <t>ChargeItemDefinition.extension:PricingSection29</t>
@@ -1782,12 +1814,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="58.1171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.82421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1795,7 +1827,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4909,43 +4941,41 @@
         <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4993,7 +5023,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5002,13 +5032,13 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>137</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -5020,35 +5050,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>237</v>
@@ -5056,12 +5088,8 @@
       <c r="M29" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5109,28 +5137,28 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>236</v>
+        <v>136</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5138,14 +5166,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5158,25 +5186,25 @@
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5225,7 +5253,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5237,27 +5265,27 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5265,7 +5293,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
@@ -5280,18 +5308,20 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5339,10 +5369,10 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>87</v>
@@ -5357,21 +5387,21 @@
         <v>85</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5382,10 +5412,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5394,18 +5424,20 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5453,13 +5485,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5471,21 +5503,21 @@
         <v>85</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5496,10 +5528,10 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5508,15 +5540,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5565,13 +5599,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5583,35 +5617,35 @@
         <v>85</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5620,7 +5654,7 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>269</v>
@@ -5628,7 +5662,9 @@
       <c r="M34" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5677,13 +5713,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5695,7 +5731,7 @@
         <v>85</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5706,14 +5742,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5732,13 +5768,13 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>268</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5789,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5816,45 +5852,43 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>278</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5879,13 +5913,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5903,13 +5937,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5921,10 +5955,10 @@
         <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -5932,21 +5966,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5958,20 +5992,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6019,13 +6049,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6037,53 +6067,53 @@
         <v>85</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>293</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6109,13 +6139,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6133,10 +6163,10 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>87</v>
@@ -6151,21 +6181,21 @@
         <v>85</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6179,7 +6209,7 @@
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6188,19 +6218,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6249,7 +6279,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6267,35 +6297,35 @@
         <v>85</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6304,16 +6334,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6363,13 +6393,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6381,10 +6411,10 @@
         <v>85</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6392,10 +6422,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6418,18 +6448,20 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6477,7 +6509,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6495,21 +6527,21 @@
         <v>85</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6523,7 +6555,7 @@
         <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6532,20 +6564,18 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>323</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6593,7 +6623,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6611,7 +6641,7 @@
         <v>85</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6620,12 +6650,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6636,10 +6666,10 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6648,16 +6678,16 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6683,13 +6713,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6707,13 +6737,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6725,7 +6755,7 @@
         <v>85</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6736,21 +6766,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6759,20 +6789,22 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6821,13 +6853,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6839,21 +6871,21 @@
         <v>85</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6864,7 +6896,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6873,19 +6905,19 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6911,13 +6943,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6935,13 +6967,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6953,25 +6985,25 @@
         <v>85</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6990,19 +7022,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7051,7 +7081,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7069,21 +7099,21 @@
         <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7103,23 +7133,21 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>357</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7167,7 +7195,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7185,21 +7213,21 @@
         <v>85</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7213,25 +7241,29 @@
         <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7255,13 +7287,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7279,7 +7311,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7297,21 +7329,21 @@
         <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7322,30 +7354,32 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K49" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7393,13 +7427,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7411,21 +7445,21 @@
         <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7436,7 +7470,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>88</v>
@@ -7445,20 +7479,18 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>374</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7483,13 +7515,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7507,13 +7539,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7534,7 +7566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>375</v>
       </c>
@@ -7550,10 +7582,10 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7562,15 +7594,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>252</v>
+        <v>376</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7619,22 +7653,22 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7646,7 +7680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>380</v>
       </c>
@@ -7655,7 +7689,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7665,7 +7699,7 @@
         <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -7674,16 +7708,16 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>131</v>
+        <v>381</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7733,7 +7767,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7745,10 +7779,10 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7762,33 +7796,33 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>386</v>
@@ -7796,12 +7830,8 @@
       <c r="M53" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N53" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7855,16 +7885,16 @@
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7878,21 +7908,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7904,15 +7934,17 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7961,22 +7993,22 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK54" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7990,42 +8022,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8073,19 +8109,19 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -8102,10 +8138,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8113,7 +8149,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
@@ -8128,17 +8164,15 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8187,7 +8221,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8214,12 +8248,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8230,10 +8264,10 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8242,13 +8276,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8299,13 +8333,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8328,10 +8362,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8354,15 +8388,17 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8411,7 +8447,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8423,10 +8459,10 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8438,16 +8474,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8457,7 +8493,7 @@
         <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8466,17 +8502,15 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>131</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8525,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8537,10 +8571,10 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
@@ -8554,33 +8588,33 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>386</v>
@@ -8588,12 +8622,8 @@
       <c r="M60" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8647,16 +8677,16 @@
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
@@ -8670,14 +8700,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8696,16 +8726,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>371</v>
+        <v>131</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>374</v>
+        <v>243</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8755,7 +8785,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8767,10 +8797,10 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
@@ -8784,42 +8814,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8867,22 +8901,22 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -8896,14 +8930,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8922,16 +8956,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>131</v>
+        <v>381</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8981,7 +9015,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8993,10 +9027,10 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
@@ -9010,33 +9044,33 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>386</v>
@@ -9044,12 +9078,8 @@
       <c r="M64" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9103,16 +9133,16 @@
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
@@ -9126,21 +9156,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9152,15 +9182,17 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9209,22 +9241,22 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
@@ -9238,42 +9270,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9321,19 +9357,19 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -9350,10 +9386,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9361,7 +9397,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>87</v>
@@ -9376,17 +9412,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9435,7 +9469,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9462,12 +9496,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9478,10 +9512,10 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9490,13 +9524,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9547,13 +9581,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -9576,10 +9610,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9602,15 +9636,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>376</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9659,7 +9695,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9671,10 +9707,10 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9686,16 +9722,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9705,7 +9741,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -9714,17 +9750,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>131</v>
+        <v>381</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9773,7 +9807,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9785,10 +9819,10 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9802,33 +9836,33 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>386</v>
@@ -9836,12 +9870,8 @@
       <c r="M71" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N71" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9895,16 +9925,16 @@
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -9916,26 +9946,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -9944,15 +9974,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9977,13 +10009,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>429</v>
+        <v>21</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10001,22 +10033,22 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -10030,42 +10062,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>326</v>
+        <v>131</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10113,19 +10149,19 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>85</v>
@@ -10140,12 +10176,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10153,13 +10189,13 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -10168,13 +10204,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>377</v>
+        <v>438</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10201,13 +10237,13 @@
         <v>21</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>21</v>
@@ -10225,10 +10261,10 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>87</v>
@@ -10237,10 +10273,10 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10254,21 +10290,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10280,17 +10316,15 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>131</v>
+        <v>336</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10327,34 +10361,34 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>379</v>
+        <v>85</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
@@ -10368,10 +10402,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10382,7 +10416,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10391,23 +10425,19 @@
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>438</v>
+        <v>262</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10455,22 +10485,22 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10491,14 +10521,14 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -10507,23 +10537,21 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10559,34 +10587,34 @@
         <v>21</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10600,10 +10628,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10614,7 +10642,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -10623,19 +10651,23 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10683,13 +10715,13 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
@@ -10698,7 +10730,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>85</v>
+        <v>454</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10712,10 +10744,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10735,19 +10767,23 @@
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10795,7 +10831,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10810,20 +10846,244 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AL80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN79">
+  <autoFilter ref="A1:AN81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10833,7 +11093,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
